--- a/alerta_processos.xlsx
+++ b/alerta_processos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0070622-73.2011.8.17.0001</t>
+          <t>0080588-93.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Seção A da 16ª Vara Cível da Capital</t>
+          <t>Seção A da 23ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12/05/2025</t>
+          <t>13/05/2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,11 +513,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Maria Simone Nascimento Carreiro</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>7</v>
@@ -535,12 +535,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0080588-93.2019.8.17.2001</t>
+          <t>0007195-56.2019.8.17.2480</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seção A da 23ª Vara Cível da Capital</t>
+          <t>3ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -579,17 +579,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0016959-88.2006.8.17.0001</t>
+          <t>0021977-89.2015.8.17.2001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seção A da 23ª Vara Cível da Capital</t>
+          <t>Seção A da 5ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,14 +599,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Maria Simone Nascimento Carreiro</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -621,17 +621,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0007195-56.2019.8.17.2480</t>
+          <t>0001616-69.2018.8.17.2640</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca de Caruaru</t>
+          <t>3ª Vara Cível da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -660,17 +660,15 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0021977-89.2015.8.17.2001</t>
+          <t>0000788-10.2017.8.17.2640</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seção A da 5ª Vara Cível da Capital</t>
+          <t>2ª Vara Cível da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -680,7 +678,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,7 +690,7 @@
         <v>34</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -707,12 +705,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0001616-69.2018.8.17.2640</t>
+          <t>0001319-13.2025.8.17.2480</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca de Garanhuns</t>
+          <t>6ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -734,7 +732,7 @@
         <v>34</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,12 +747,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0000788-10.2017.8.17.2640</t>
+          <t>0008497-68.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Garanhuns</t>
+          <t>Seção A da 21ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -788,15 +786,17 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0001319-13.2025.8.17.2480</t>
+          <t>0012055-95.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6ª Vara Cível da Comarca de Caruaru</t>
+          <t>2ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -833,12 +833,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0008497-68.2020.8.17.2001</t>
+          <t>0002021-27.2023.8.17.2480</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seção A da 21ª Vara Cível da Capital</t>
+          <t>2ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0012055-95.2022.8.17.2480</t>
+          <t>0025713-76.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Caruaru</t>
+          <t>Seção A da 24ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -897,14 +897,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Jonas Ferreira Da Paixao</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -919,17 +919,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0002021-27.2023.8.17.2480</t>
+          <t>0060611-81.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Caruaru</t>
+          <t>Seção B da 36ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -958,39 +958,37 @@
       <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0025713-76.2019.8.17.2001</t>
+          <t>0013423-53.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seção A da 24ª Vara Cível da Capital</t>
+          <t>Seção A da 36ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jonas Ferreira Da Paixao</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1002,62 +1000,64 @@
       <c r="B14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0060611-81.2020.8.17.2001</t>
+          <t>0005589-74.2017.8.17.3090</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seção B da 36ª Vara Cível da Capital</t>
+          <t>2ª Vara Cível da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Juliane De Oliveira Maciel</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0013423-53.2024.8.17.2001</t>
+          <t>0148031-96.2009.8.17.0001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Seção A da 36ª Vara Cível da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1067,125 +1067,125 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Nathalia Fontenele Lima</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0005589-74.2017.8.17.3090</t>
+          <t>0031032-84.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Paulista</t>
+          <t>5ª Vara de Família e Registro Civil da Capital</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Juliane De Oliveira Maciel</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0148031-96.2009.8.17.0001</t>
+          <t>0001531-19.2021.8.17.3080</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Comarca de Paudalho</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nathalia Fontenele Lima</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0031032-84.2014.8.17.0001</t>
+          <t>0001672-51.2011.8.17.0570</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5ª Vara de Família e Registro Civil da Capital</t>
+          <t>1ª Vara da Comarca de Escada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1195,64 +1195,62 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Gustavo Mendes Da Hora</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0001531-19.2021.8.17.3080</t>
+          <t>0026284-46.2022.8.17.2420</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2ª Vara da Comarca de Paudalho</t>
+          <t>3ª Vara Cível da Comarca de Camaragibe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1261,17 +1259,17 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0001672-51.2011.8.17.0570</t>
+          <t>0002145-36.2023.8.17.2730</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1ª Vara da Comarca de Escada</t>
+          <t>2ª Vara Cível da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1281,39 +1279,39 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Gustavo Mendes Da Hora</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0000375-77.2020.8.17.3420</t>
+          <t>0005986-96.2023.8.17.2420</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Tabira</t>
+          <t>3ª Vara Cível da Comarca de Camaragibe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1323,39 +1321,39 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Valeria Perpetua Evaristo Da Costa</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0002099-30.2020.8.17.2220</t>
+          <t>0003928-97.2022.8.17.2730</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1ª Vara Cível da Comarca de Arcoverde</t>
+          <t>2ª Vara Cível da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1365,39 +1363,39 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valnete Lima Do Espirito Santo</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0000810-98.2023.8.17.2950</t>
+          <t>0004260-65.2013.8.17.0730</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Mirandiba</t>
+          <t>2ª Vara Cível da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1407,39 +1405,39 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valnete Lima Do Espirito Santo</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0000580-22.2023.8.17.3220</t>
+          <t>0000258-89.2021.8.17.2470</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1ª Vara Cível da Comarca de Salgueiro</t>
+          <t>3ª Vara Cível da Comarca de Carpina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18/05/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1449,14 +1447,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valnete Lima Do Espirito Santo</t>
+          <t>Ana Paula Alice Da Silva Santos</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1466,22 +1464,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0001010-88.2021.8.17.2170</t>
+          <t>0000049-82.2024.8.17.2190</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Aliança</t>
+          <t>Vara Única da Comarca de Amaraji</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1495,10 +1493,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1508,22 +1506,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0000233-96.2021.8.17.2140</t>
+          <t>0000411-52.2023.8.17.2600</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1ª Vara da Comarca de Água Preta</t>
+          <t>1ª Vara da Comarca de Timbaúba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1537,10 +1535,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1550,22 +1548,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0016472-33.2022.8.17.2370</t>
+          <t>0002218-80.2021.8.17.2470</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4ª Vara Cível da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara Cível da Comarca de Carpina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1579,10 +1577,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1592,22 +1590,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0000738-93.2011.8.17.0570</t>
+          <t>0001695-39.2019.8.17.2470</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2ª Vara da Comarca de Escada</t>
+          <t>3ª Vara Cível da Comarca de Carpina</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1621,10 +1619,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1634,12 +1632,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0003886-52.2022.8.17.2470</t>
+          <t>0002614-96.2017.8.17.2470</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1649,7 +1647,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1663,10 +1661,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1676,12 +1674,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0003626-72.2022.8.17.2470</t>
+          <t>0003560-92.2022.8.17.2470</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1691,7 +1689,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1705,10 +1703,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1718,22 +1716,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0026284-46.2022.8.17.2420</t>
+          <t>0001452-88.2024.8.17.3030</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca de Camaragibe</t>
+          <t>2ª Vara Cível da Comarca de Palmares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1747,10 +1745,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -1760,22 +1758,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0002145-36.2023.8.17.2730</t>
+          <t>0003076-77.2022.8.17.2470</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Ipojuca</t>
+          <t>1ª Vara Cível da Comarca de Carpina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1789,10 +1787,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1802,22 +1800,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0005986-96.2023.8.17.2420</t>
+          <t>0000149-80.2021.8.17.3600</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca de Camaragibe</t>
+          <t>Vara Única do Arquipélago de Fernando de Noronha</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>16/05/2025</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1831,513 +1829,9 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>10</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0003928-97.2022.8.17.2730</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2ª Vara Cível da Comarca de Ipojuca</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>14/05/2025</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>34</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>11</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0004260-65.2013.8.17.0730</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2ª Vara Cível da Comarca de Ipojuca</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>14/05/2025</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>34</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>12</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0000258-89.2021.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>14/05/2025</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>34</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>13</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0000049-82.2024.8.17.2190</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Vara Única da Comarca de Amaraji</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>32</v>
-      </c>
-      <c r="J37" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0000411-52.2023.8.17.2600</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1ª Vara da Comarca de Timbaúba</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>32</v>
-      </c>
-      <c r="J38" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>15</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0002218-80.2021.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>32</v>
-      </c>
-      <c r="J39" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>16</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0001695-39.2019.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>3ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>32</v>
-      </c>
-      <c r="J40" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>17</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0002614-96.2017.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>32</v>
-      </c>
-      <c r="J41" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>18</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0003560-92.2022.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>32</v>
-      </c>
-      <c r="J42" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>19</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0001452-88.2024.8.17.3030</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2ª Vara Cível da Comarca de Palmares</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>32</v>
-      </c>
-      <c r="J43" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>20</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0003076-77.2022.8.17.2470</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1ª Vara Cível da Comarca de Carpina</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>32</v>
-      </c>
-      <c r="J44" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>5ª CC</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>21</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0000149-80.2021.8.17.3600</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Vara Única do Arquipélago de Fernando de Noronha</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>16/05/2025</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Ana Paula Alice Da Silva Santos</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>32</v>
-      </c>
-      <c r="J45" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2352,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2405,21 +1899,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0009436-76.2018.8.17.2370</t>
+          <t>0045746-59.2008.8.17.0001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2440,21 +1934,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0010732-48.2020.8.17.2990</t>
+          <t>0003033-30.2025.8.17.2990</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2479,12 +1973,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0045746-59.2008.8.17.0001</t>
+          <t>0006057-61.2015.8.17.0001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2514,17 +2008,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0003033-30.2025.8.17.2990</t>
+          <t>0032225-41.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2554,12 +2048,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0006057-61.2015.8.17.0001</t>
+          <t>0025576-94.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2584,12 +2078,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0032225-41.2020.8.17.2001</t>
+          <t>0017917-39.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2619,17 +2113,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0025576-94.2019.8.17.2001</t>
+          <t>0012736-57.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>4ª Vara de Sucessões e Registros Públicos da Capital</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2654,17 +2148,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0017917-39.2016.8.17.2001</t>
+          <t>0005937-23.2025.8.17.2990</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2689,17 +2183,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0012736-57.2016.8.17.2001</t>
+          <t>0007385-31.2025.8.17.2990</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2724,17 +2218,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0005937-23.2025.8.17.2990</t>
+          <t>0142012-74.2009.8.17.0001</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2759,12 +2253,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0007385-31.2025.8.17.2990</t>
+          <t>0022319-28.2024.8.17.2990</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2799,12 +2293,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0142012-74.2009.8.17.0001</t>
+          <t>0009389-41.2025.8.17.2990</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2825,21 +2319,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0022319-28.2024.8.17.2990</t>
+          <t>0000229-15.2008.8.17.0750</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>Vara Única da Comarca de Itaíba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2860,21 +2354,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0009389-41.2025.8.17.2990</t>
+          <t>0000687-80.2023.8.17.3280</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>2ª Vara da Comarca de São Bento do Una</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2899,17 +2393,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0000229-15.2008.8.17.0750</t>
+          <t>0002228-86.2017.8.17.3110</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Itaíba</t>
+          <t>1ª Vara Cível da Comarca de Pesqueira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2934,17 +2428,17 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0000687-80.2023.8.17.3280</t>
+          <t>0000051-84.2018.8.17.2700</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2ª Vara da Comarca de São Bento do Una</t>
+          <t>Vara Única da Comarca de Altinho</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2965,26 +2459,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0002228-86.2017.8.17.3110</t>
+          <t>0000213-83.2021.8.17.0660</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1ª Vara Cível da Comarca de Pesqueira</t>
+          <t>Vara Criminal da Comarca de Goiana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2994,32 +2488,32 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0000051-84.2018.8.17.2700</t>
+          <t>0024854-54.2013.8.17.0810</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Altinho</t>
+          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3029,44 +2523,42 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0003251-23.2024.8.17.3110</t>
+          <t>0003633-68.2020.8.17.0810</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1ª Vara Cível da Comarca de Pesqueira</t>
+          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -3076,22 +2568,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0000466-14.2016.8.17.1350</t>
+          <t>0001411-50.2020.8.17.0480</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de São Lourenço da Mata</t>
+          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3101,7 +2593,7 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -3111,22 +2603,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0055938-07.2015.8.17.0001</t>
+          <t>0000751-98.2020.8.17.0660</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8ª Vara Criminal da Capital</t>
+          <t>Vara Criminal da Comarca de Goiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3136,7 +2628,7 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -3146,22 +2638,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0002295-50.2018.8.17.0480</t>
+          <t>0003271-89.2021.8.17.3410</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara Criminal da Comarca de Surubim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3171,7 +2663,7 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -3181,22 +2673,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0000175-09.2022.8.17.2480</t>
+          <t>0000326-77.2024.8.17.5980</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara Criminal da Comarca de Goiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3206,7 +2698,7 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -3216,22 +2708,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0011528-19.2019.8.17.0001</t>
+          <t>0000331-52.2021.8.17.5480</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Capital</t>
+          <t>3ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3241,7 +2733,7 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -3251,17 +2743,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0000213-83.2021.8.17.0660</t>
+          <t>0026289-58.2016.8.17.0810</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Goiana</t>
+          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3286,17 +2778,17 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0024854-54.2013.8.17.0810</t>
+          <t>0001550-04.2019.8.17.1590</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara Criminal da Comarca de Vitória de Santo Antão</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3321,22 +2813,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0003633-68.2020.8.17.0810</t>
+          <t>0004849-55.2018.8.17.0480</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3346,7 +2838,7 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -3356,22 +2848,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0001411-50.2020.8.17.0480</t>
+          <t>0001017-09.2021.8.17.0480</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
+          <t>3ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3381,7 +2873,7 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -3391,22 +2883,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0000751-98.2020.8.17.0660</t>
+          <t>0001935-30.2021.8.17.5001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Goiana</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3416,7 +2908,7 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -3426,22 +2918,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0003271-89.2021.8.17.3410</t>
+          <t>0000758-24.2021.8.17.4001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Surubim</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3451,7 +2943,7 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -3461,22 +2953,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0000326-77.2024.8.17.5980</t>
+          <t>0008778-96.2018.8.17.0480</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Goiana</t>
+          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3486,7 +2978,7 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -3496,22 +2988,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0000331-52.2021.8.17.5480</t>
+          <t>0001201-96.2020.8.17.0480</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3521,7 +3013,7 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -3531,22 +3023,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0026289-58.2016.8.17.0810</t>
+          <t>0001033-94.2020.8.17.0480</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3556,7 +3048,7 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -3566,22 +3058,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0001550-04.2019.8.17.1590</t>
+          <t>0004750-51.2019.8.17.0480</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Vitória de Santo Antão</t>
+          <t>3ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3591,7 +3083,7 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -3601,17 +3093,17 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0004849-55.2018.8.17.0480</t>
+          <t>0002707-54.2022.8.17.5810</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
+          <t>3ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3636,17 +3128,17 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0001017-09.2021.8.17.0480</t>
+          <t>0000153-19.2023.8.17.2640</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3671,17 +3163,17 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0001935-30.2021.8.17.5001</t>
+          <t>0000094-82.2020.8.17.1590</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>Vara Criminal da Comarca de Gravatá</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3706,17 +3198,17 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0000758-24.2021.8.17.4001</t>
+          <t>0000458-42.2021.8.17.1130</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>1ª Vara Criminal da Comarca Petrolina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3741,17 +3233,17 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0008778-96.2018.8.17.0480</t>
+          <t>0004665-30.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
+          <t>1ª Vara Criminal da Comarca Petrolina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3776,17 +3268,17 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0001201-96.2020.8.17.0480</t>
+          <t>0023121-52.2022.8.17.2810</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3811,17 +3303,17 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0001033-94.2020.8.17.0480</t>
+          <t>0000601-30.2011.8.17.0500</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara Criminal da Comarca de Gravatá</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3846,17 +3338,17 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0004750-51.2019.8.17.0480</t>
+          <t>0010269-79.2003.8.17.1090</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>2ª Vara Criminal da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3881,17 +3373,17 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0002707-54.2022.8.17.5810</t>
+          <t>0001454-89.2020.8.17.0640</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3916,17 +3408,17 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0000153-19.2023.8.17.2640</t>
+          <t>0002337-77.2022.8.17.5001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3951,17 +3443,17 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0000094-82.2020.8.17.1590</t>
+          <t>0001432-88.2010.8.17.1090</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>2ª Vara Criminal da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3986,17 +3478,17 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0000458-42.2021.8.17.1130</t>
+          <t>0000908-17.2015.8.17.0670</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca Petrolina</t>
+          <t>Vara Criminal da Comarca de Gravatá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4021,17 +3513,17 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0004665-30.2023.8.17.3130</t>
+          <t>0005016-50.2022.8.17.5001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca Petrolina</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4056,17 +3548,17 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0023121-52.2022.8.17.2810</t>
+          <t>0009002-45.2020.8.17.0001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>13ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4091,17 +3583,17 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0000601-30.2011.8.17.0500</t>
+          <t>0002979-14.2023.8.17.5810</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4126,17 +3618,17 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0010269-79.2003.8.17.1090</t>
+          <t>0001410-65.2020.8.17.0480</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Paulista</t>
+          <t>2ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4161,17 +3653,17 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0001454-89.2020.8.17.0640</t>
+          <t>0011659-51.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4196,17 +3688,17 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0002337-77.2022.8.17.5001</t>
+          <t>0001332-37.2021.8.17.0480</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>3ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4231,17 +3723,17 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0001432-88.2010.8.17.1090</t>
+          <t>0001245-07.2024.8.17.4480</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Paulista</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4266,17 +3758,17 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0000908-17.2015.8.17.0670</t>
+          <t>0002243-43.2022.8.17.4480</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4301,17 +3793,17 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0005016-50.2022.8.17.5001</t>
+          <t>0000680-13.2019.8.17.0990</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>3ª Vara Criminal da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4336,17 +3828,17 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0009002-45.2020.8.17.0001</t>
+          <t>0002342-42.2018.8.17.1250</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>13ª Vara Criminal da Capital</t>
+          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4367,26 +3859,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0002979-14.2023.8.17.5810</t>
+          <t>0014108-26.2025.8.17.2001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4396,102 +3888,106 @@
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>58</v>
-      </c>
-      <c r="C59" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0001410-65.2020.8.17.0480</t>
+          <t>0001299-57.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>59</v>
-      </c>
-      <c r="C60" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0011659-51.2015.8.17.0480</t>
+          <t>0000623-71.2023.8.17.2730</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0001332-37.2021.8.17.0480</t>
+          <t>0006530-46.2007.8.17.0480</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4501,32 +3997,32 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0001245-07.2024.8.17.4480</t>
+          <t>0042476-89.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4536,32 +4032,32 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0002243-43.2022.8.17.4480</t>
+          <t>0054814-95.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4571,32 +4067,32 @@
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0000680-13.2019.8.17.0990</t>
+          <t>0003106-49.2008.8.17.1130</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4606,32 +4102,32 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0002342-42.2018.8.17.1250</t>
+          <t>0004644-35.2024.8.17.2640</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>22/05/2025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4641,7 +4137,7 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
@@ -4651,17 +4147,17 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0014108-26.2025.8.17.2001</t>
+          <t>0001061-29.2005.8.17.0370</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4686,19 +4182,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0001299-57.2015.8.17.0480</t>
+          <t>0005863-88.2021.8.17.2640</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4708,7 +4204,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -4723,19 +4219,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0000623-71.2023.8.17.2730</t>
+          <t>0011525-62.2023.8.17.2640</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4760,17 +4256,17 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0006530-46.2007.8.17.0480</t>
+          <t>0029731-41.2019.8.17.2810</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4795,17 +4291,17 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0042476-89.2018.8.17.2001</t>
+          <t>0012072-58.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4830,17 +4326,17 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0054814-95.2018.8.17.2001</t>
+          <t>0008042-11.2017.8.17.2001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4865,17 +4361,17 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0003106-49.2008.8.17.1130</t>
+          <t>0010088-89.2008.8.17.0480</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4900,17 +4396,17 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0004644-35.2024.8.17.2640</t>
+          <t>0010672-33.2012.8.17.1090</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4935,17 +4431,17 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0001061-29.2005.8.17.0370</t>
+          <t>0018833-74.2007.8.17.0001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4970,19 +4466,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0005863-88.2021.8.17.2640</t>
+          <t>0010563-86.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5007,34 +4503,32 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23</v>
-      </c>
-      <c r="C76" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0011525-62.2023.8.17.2640</t>
+          <t>0009803-61.2017.8.17.0810</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77">
@@ -5044,12 +4538,12 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0029731-41.2019.8.17.2810</t>
+          <t>0032234-93.2023.8.17.2810</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5059,7 +4553,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5069,7 +4563,7 @@
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -5079,22 +4573,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0012072-58.2021.8.17.3130</t>
+          <t>0003873-91.2020.8.17.2480</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5104,7 +4598,7 @@
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79">
@@ -5114,22 +4608,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0008042-11.2017.8.17.2001</t>
+          <t>0047811-55.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5139,7 +4633,7 @@
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -5149,22 +4643,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0010088-89.2008.8.17.0480</t>
+          <t>0014331-85.2010.8.17.0810</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5174,7 +4668,7 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
@@ -5184,32 +4678,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>28</v>
-      </c>
-      <c r="C81" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0010672-33.2012.8.17.1090</t>
+          <t>0020917-82.2019.8.17.2990</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -5219,22 +4715,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0018833-74.2007.8.17.0001</t>
+          <t>0042254-24.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5244,7 +4740,7 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -5254,34 +4750,32 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>30</v>
-      </c>
-      <c r="C83" t="n">
-        <v>4</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0010563-86.2019.8.17.3090</t>
+          <t>0014773-52.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>22/05/2025</t>
+          <t>23/05/2025</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
@@ -5291,17 +4785,17 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0009803-61.2017.8.17.0810</t>
+          <t>0000778-83.2016.8.17.0640</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5326,17 +4820,17 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0032234-93.2023.8.17.2810</t>
+          <t>0001024-13.2003.8.17.0001</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5361,17 +4855,17 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0003873-91.2020.8.17.2480</t>
+          <t>0016259-49.2005.8.17.0001</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5396,17 +4890,17 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0047811-55.2019.8.17.2001</t>
+          <t>0042363-32.2012.8.17.0810</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5431,12 +4925,12 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0014331-85.2010.8.17.0810</t>
+          <t>0030807-95.2022.8.17.2810</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5466,19 +4960,17 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>36</v>
-      </c>
-      <c r="C89" t="n">
-        <v>5</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0020917-82.2019.8.17.2990</t>
+          <t>0003058-60.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5488,7 +4980,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -5503,17 +4995,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37</v>
-      </c>
-      <c r="C90" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0042254-24.2018.8.17.2001</t>
+          <t>0167080-83.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5523,7 +5017,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -5538,22 +5032,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0014773-52.2019.8.17.2001</t>
+          <t>0020079-63.2020.8.17.2810</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5563,7 +5057,7 @@
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -5573,22 +5067,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0000778-83.2016.8.17.0640</t>
+          <t>0023238-95.2003.8.17.0001</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5598,7 +5092,7 @@
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -5608,22 +5102,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0001024-13.2003.8.17.0001</t>
+          <t>0007041-04.2020.8.17.2480</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5633,7 +5127,7 @@
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -5643,22 +5137,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0016259-49.2005.8.17.0001</t>
+          <t>0045830-60.2008.8.17.0001</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5668,7 +5162,7 @@
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -5678,22 +5172,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0042363-32.2012.8.17.0810</t>
+          <t>0006236-98.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5703,7 +5197,7 @@
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -5713,22 +5207,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0030807-95.2022.8.17.2810</t>
+          <t>0101563-63.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5738,7 +5232,7 @@
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -5748,22 +5242,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0003058-60.2021.8.17.2480</t>
+          <t>0036036-54.2004.8.17.0001</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5773,7 +5267,7 @@
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -5783,34 +5277,32 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>45</v>
-      </c>
-      <c r="C98" t="n">
-        <v>3</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0167080-83.2022.8.17.2001</t>
+          <t>0063500-71.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -5820,17 +5312,17 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0020079-63.2020.8.17.2810</t>
+          <t>0011919-81.2013.8.17.0001</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
+          <t>4ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5855,17 +5347,17 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0023238-95.2003.8.17.0001</t>
+          <t>0071550-92.2022.8.17.2990</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5890,17 +5382,17 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0007041-04.2020.8.17.2480</t>
+          <t>0000939-18.2019.8.17.3250</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5925,17 +5417,17 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0045830-60.2008.8.17.0001</t>
+          <t>0001673-11.1998.8.17.0370</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5960,17 +5452,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>50</v>
-      </c>
-      <c r="C103" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3</v>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0006236-98.2019.8.17.3090</t>
+          <t>0007935-60.2011.8.17.0001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5980,7 +5474,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -5995,17 +5489,17 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0101563-63.2024.8.17.2001</t>
+          <t>0009536-96.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6030,17 +5524,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>52</v>
-      </c>
-      <c r="C105" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="C105" t="n">
+        <v>6</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0036036-54.2004.8.17.0001</t>
+          <t>0021227-49.2023.8.17.2990</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6050,7 +5546,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -6065,12 +5561,12 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0063500-71.2021.8.17.2001</t>
+          <t>0096778-29.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6100,17 +5596,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>54</v>
-      </c>
-      <c r="C107" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0011919-81.2013.8.17.0001</t>
+          <t>0054788-92.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6120,7 +5618,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -6135,17 +5633,17 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0071550-92.2022.8.17.2990</t>
+          <t>0040404-96.2010.8.17.0001</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6170,17 +5668,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>56</v>
-      </c>
-      <c r="C109" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0000939-18.2019.8.17.3250</t>
+          <t>0011449-86.2024.8.17.3130</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Santa Cruz do Capibaribe</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6190,7 +5690,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -6205,32 +5705,34 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>57</v>
-      </c>
-      <c r="C110" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C110" t="n">
+        <v>6</v>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0001673-11.1998.8.17.0370</t>
+          <t>0032180-34.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111">
@@ -6240,34 +5742,32 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>58</v>
-      </c>
-      <c r="C111" t="n">
-        <v>4</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0007935-60.2011.8.17.0001</t>
+          <t>0009823-18.2019.8.17.2480</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112">
@@ -6277,32 +5777,34 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>59</v>
-      </c>
-      <c r="C112" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="C112" t="n">
+        <v>7</v>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0009536-96.2014.8.17.0001</t>
+          <t>0133240-48.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
@@ -6312,24 +5814,24 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0021227-49.2023.8.17.2990</t>
+          <t>0020055-68.2020.8.17.3090</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6339,7 +5841,7 @@
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114">
@@ -6349,22 +5851,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0096778-29.2022.8.17.2001</t>
+          <t>0043827-26.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6374,7 +5876,7 @@
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115">
@@ -6384,34 +5886,32 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>62</v>
-      </c>
-      <c r="C115" t="n">
-        <v>5</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0054788-92.2021.8.17.2001</t>
+          <t>0003306-41.2017.8.17.1130</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116">
@@ -6421,22 +5921,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0040404-96.2010.8.17.0001</t>
+          <t>0010243-77.2011.8.17.1130</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6446,7 +5946,7 @@
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117">
@@ -6456,14 +5956,12 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>64</v>
-      </c>
-      <c r="C117" t="n">
-        <v>6</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0011449-86.2024.8.17.3130</t>
+          <t>0013275-55.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6473,17 +5971,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118">
@@ -6493,19 +5991,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0032180-34.2021.8.17.3090</t>
+          <t>0018948-58.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6515,7 +6013,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -6530,17 +6028,17 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0009823-18.2019.8.17.2480</t>
+          <t>0022852-54.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6565,19 +6063,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0133240-48.2023.8.17.2001</t>
+          <t>0010765-59.2021.8.17.2810</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6602,19 +6100,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0020055-68.2020.8.17.3090</t>
+          <t>0114419-59.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6639,17 +6137,17 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0043827-26.2021.8.17.3090</t>
+          <t>0010702-70.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6674,17 +6172,17 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0003306-41.2017.8.17.1130</t>
+          <t>0004024-33.2018.8.17.2640</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6709,17 +6207,17 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0010243-77.2011.8.17.1130</t>
+          <t>0030684-31.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6744,17 +6242,17 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0013275-55.2021.8.17.3130</t>
+          <t>0004453-24.2023.8.17.2640</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6779,19 +6277,17 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>73</v>
-      </c>
-      <c r="C126" t="n">
-        <v>9</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0018948-58.2023.8.17.3130</t>
+          <t>0048248-68.2008.8.17.0001</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6801,7 +6297,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6816,17 +6312,17 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0022852-54.2018.8.17.2001</t>
+          <t>0181715-07.2012.8.17.0001</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6851,19 +6347,17 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>75</v>
-      </c>
-      <c r="C128" t="n">
-        <v>10</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0010765-59.2021.8.17.2810</t>
+          <t>0103809-43.2009.8.17.0001</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6873,7 +6367,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6888,19 +6382,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0114419-59.2024.8.17.2001</t>
+          <t>0011234-12.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6925,17 +6419,17 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0010702-70.2020.8.17.2001</t>
+          <t>0001493-27.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6960,17 +6454,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>78</v>
-      </c>
-      <c r="C131" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7</v>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0004024-33.2018.8.17.2640</t>
+          <t>0125045-74.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6980,7 +6476,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6995,17 +6491,17 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0030684-31.2024.8.17.2001</t>
+          <t>0002164-94.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7030,17 +6526,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>80</v>
-      </c>
-      <c r="C133" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="C133" t="n">
+        <v>13</v>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0004453-24.2023.8.17.2640</t>
+          <t>0018968-75.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7050,7 +6548,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -7065,17 +6563,17 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0048248-68.2008.8.17.0001</t>
+          <t>0015291-78.2013.8.17.0990</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7100,17 +6598,17 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0181715-07.2012.8.17.0001</t>
+          <t>0004393-95.2017.8.17.2370</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7135,17 +6633,17 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0103809-43.2009.8.17.0001</t>
+          <t>0004882-72.2015.8.17.0990</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7170,19 +6668,17 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>84</v>
-      </c>
-      <c r="C137" t="n">
-        <v>12</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0011234-12.2019.8.17.3090</t>
+          <t>0031751-64.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7192,7 +6688,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -7207,17 +6703,17 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0001493-27.2022.8.17.2480</t>
+          <t>0012360-66.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7242,19 +6738,17 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>86</v>
-      </c>
-      <c r="C139" t="n">
-        <v>8</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0125045-74.2023.8.17.2001</t>
+          <t>0001470-28.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7264,7 +6758,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -7279,17 +6773,17 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0002164-94.2019.8.17.2370</t>
+          <t>0019067-45.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7314,19 +6808,17 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>88</v>
-      </c>
-      <c r="C141" t="n">
-        <v>13</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0018968-75.2022.8.17.2001</t>
+          <t>0006929-57.2020.8.17.2990</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7336,7 +6828,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -7351,22 +6843,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0015291-78.2013.8.17.0990</t>
+          <t>0162784-18.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -7376,7 +6868,7 @@
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -7386,22 +6878,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0004393-95.2017.8.17.2370</t>
+          <t>0003563-70.2009.8.17.1090</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -7411,7 +6903,7 @@
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144">
@@ -7421,22 +6913,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0004882-72.2015.8.17.0990</t>
+          <t>0013399-19.2023.8.17.2370</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -7446,7 +6938,7 @@
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145">
@@ -7456,22 +6948,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0031751-64.2019.8.17.2370</t>
+          <t>0144859-88.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -7481,7 +6973,7 @@
       </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146">
@@ -7491,22 +6983,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0012360-66.2019.8.17.2001</t>
+          <t>0000474-60.2025.8.17.2001</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -7516,7 +7008,7 @@
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147">
@@ -7526,22 +7018,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0001470-28.2019.8.17.2370</t>
+          <t>0048893-58.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7551,7 +7043,7 @@
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
@@ -7561,22 +7053,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0019067-45.2022.8.17.2001</t>
+          <t>0021145-14.2020.8.17.3090</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7586,7 +7078,7 @@
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149">
@@ -7596,22 +7088,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0006929-57.2020.8.17.2990</t>
+          <t>0000049-02.2023.8.17.2810</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -7621,7 +7113,7 @@
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -7631,17 +7123,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>97</v>
-      </c>
-      <c r="C150" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="C150" t="n">
+        <v>14</v>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0162784-18.2022.8.17.2001</t>
+          <t>0030671-06.2019.8.17.2810</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7651,7 +7145,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -7666,17 +7160,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>98</v>
-      </c>
-      <c r="C151" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="C151" t="n">
+        <v>15</v>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0003563-70.2009.8.17.1090</t>
+          <t>0043033-42.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7686,7 +7182,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7701,17 +7197,17 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0013399-19.2023.8.17.2370</t>
+          <t>0004615-15.2008.8.17.1130</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7736,17 +7232,17 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0144859-88.2018.8.17.2990</t>
+          <t>0043131-25.2019.8.17.2810</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7771,17 +7267,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>101</v>
-      </c>
-      <c r="C154" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="C154" t="n">
+        <v>8</v>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0000474-60.2025.8.17.2001</t>
+          <t>0011001-50.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7791,7 +7289,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -7806,17 +7304,17 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0048893-58.2018.8.17.2001</t>
+          <t>0000979-38.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7841,17 +7339,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>103</v>
-      </c>
-      <c r="C156" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="C156" t="n">
+        <v>9</v>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0021145-14.2020.8.17.3090</t>
+          <t>0100659-14.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7861,7 +7361,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -7876,17 +7376,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>104</v>
-      </c>
-      <c r="C157" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="C157" t="n">
+        <v>10</v>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0000049-02.2023.8.17.2810</t>
+          <t>0137949-29.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7896,7 +7398,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -7911,19 +7413,17 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>105</v>
-      </c>
-      <c r="C158" t="n">
-        <v>14</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0030671-06.2019.8.17.2810</t>
+          <t>0000542-67.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7933,7 +7433,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -7948,19 +7448,17 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>106</v>
-      </c>
-      <c r="C159" t="n">
-        <v>15</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0043033-42.2019.8.17.2001</t>
+          <t>0044705-22.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7970,7 +7468,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -7985,17 +7483,17 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0004615-15.2008.8.17.1130</t>
+          <t>0008273-86.2014.8.17.0370</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8020,17 +7518,17 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0043131-25.2019.8.17.2810</t>
+          <t>0002783-88.2011.8.17.0370</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8055,19 +7553,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0011001-50.2023.8.17.3130</t>
+          <t>0159662-60.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8092,22 +7590,22 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0000979-38.2018.8.17.2990</t>
+          <t>0012715-75.2010.8.17.0810</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -8117,7 +7615,7 @@
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164">
@@ -8127,34 +7625,32 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>111</v>
-      </c>
-      <c r="C164" t="n">
-        <v>10</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0100659-14.2022.8.17.2001</t>
+          <t>0157599-62.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165">
@@ -8164,14 +7660,12 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>112</v>
-      </c>
-      <c r="C165" t="n">
-        <v>11</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0137949-29.2023.8.17.2001</t>
+          <t>0025016-37.2002.8.17.0001</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8181,17 +7675,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166">
@@ -8201,32 +7695,34 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>113</v>
-      </c>
-      <c r="C166" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="C166" t="n">
+        <v>12</v>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0000542-67.2021.8.17.2480</t>
+          <t>0002608-75.2023.8.17.2730</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167">
@@ -8236,22 +7732,22 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0044705-22.2018.8.17.2001</t>
+          <t>0067928-62.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -8261,7 +7757,7 @@
       </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168">
@@ -8271,22 +7767,22 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0008273-86.2014.8.17.0370</t>
+          <t>0002885-17.2012.8.17.0810</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -8296,7 +7792,7 @@
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169">
@@ -8306,32 +7802,34 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>116</v>
-      </c>
-      <c r="C169" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="C169" t="n">
+        <v>13</v>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0002783-88.2011.8.17.0370</t>
+          <t>0124150-16.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170">
@@ -8341,34 +7839,34 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C170" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0159662-60.2023.8.17.2001</t>
+          <t>0023241-29.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171">
@@ -8378,17 +7876,17 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0012715-75.2010.8.17.0810</t>
+          <t>0013450-94.2011.8.17.0480</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8413,17 +7911,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>119</v>
-      </c>
-      <c r="C172" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="C172" t="n">
+        <v>14</v>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0157599-62.2023.8.17.2001</t>
+          <t>0076202-15.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8433,7 +7933,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -8448,17 +7948,17 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0025016-37.2002.8.17.0001</t>
+          <t>0055769-26.1992.8.17.0001</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8483,19 +7983,19 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C174" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0002608-75.2023.8.17.2730</t>
+          <t>0022778-58.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8505,7 +8005,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -8520,17 +8020,17 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0067928-62.2022.8.17.2001</t>
+          <t>0065967-53.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8555,17 +8055,17 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0002885-17.2012.8.17.0810</t>
+          <t>0006228-56.2007.8.17.0370</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8590,19 +8090,17 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>124</v>
-      </c>
-      <c r="C177" t="n">
-        <v>14</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0124150-16.2023.8.17.2001</t>
+          <t>0044866-95.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8612,7 +8110,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -8627,19 +8125,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C178" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0023241-29.2024.8.17.2001</t>
+          <t>0018284-50.2023.8.17.3090</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8649,7 +8147,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -8664,17 +8162,17 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0013450-94.2011.8.17.0480</t>
+          <t>0028674-55.2018.8.17.3090</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8699,19 +8197,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C180" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0076202-15.2022.8.17.2001</t>
+          <t>0060648-06.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8736,17 +8234,17 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0055769-26.1992.8.17.0001</t>
+          <t>0039607-27.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8771,19 +8269,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C182" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0022778-58.2022.8.17.2001</t>
+          <t>0021501-36.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8808,22 +8306,22 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0065967-53.2014.8.17.0001</t>
+          <t>0013621-60.2018.8.17.2370</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8833,7 +8331,7 @@
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="184">
@@ -8843,32 +8341,34 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>131</v>
-      </c>
-      <c r="C184" t="inlineStr"/>
+        <v>132</v>
+      </c>
+      <c r="C184" t="n">
+        <v>17</v>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0006228-56.2007.8.17.0370</t>
+          <t>0001813-07.2006.8.17.0001</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="185">
@@ -8878,22 +8378,22 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0044866-95.2019.8.17.2001</t>
+          <t>0001455-02.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8903,7 +8403,7 @@
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="186">
@@ -8913,34 +8413,32 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>133</v>
-      </c>
-      <c r="C186" t="n">
-        <v>16</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0018284-50.2023.8.17.3090</t>
+          <t>0005162-20.2024.8.17.2480</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187">
@@ -8950,22 +8448,22 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0028674-55.2018.8.17.3090</t>
+          <t>0005994-20.2010.8.17.1130</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -8975,7 +8473,7 @@
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188">
@@ -8985,34 +8483,34 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C188" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0060648-06.2023.8.17.2001</t>
+          <t>0090486-57.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="189">
@@ -9022,22 +8520,22 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0039607-27.2016.8.17.2001</t>
+          <t>0013636-82.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -9047,7 +8545,7 @@
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="190">
@@ -9057,34 +8555,32 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>137</v>
-      </c>
-      <c r="C190" t="n">
-        <v>18</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0021501-36.2024.8.17.2001</t>
+          <t>0025225-84.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191">
@@ -9094,17 +8590,17 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0013621-60.2018.8.17.2370</t>
+          <t>0012488-18.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9129,19 +8625,17 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>139</v>
-      </c>
-      <c r="C192" t="n">
-        <v>18</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0001813-07.2006.8.17.0001</t>
+          <t>0000485-80.2018.8.17.2730</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9151,7 +8645,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -9166,17 +8660,17 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0001455-02.2019.8.17.2001</t>
+          <t>0010172-55.2021.8.17.2640</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9201,17 +8695,17 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0005162-20.2024.8.17.2480</t>
+          <t>0036173-20.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9236,17 +8730,17 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0005994-20.2010.8.17.1130</t>
+          <t>0049199-21.2012.8.17.0810</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9271,19 +8765,17 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>143</v>
-      </c>
-      <c r="C196" t="n">
-        <v>19</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0090486-57.2024.8.17.2001</t>
+          <t>0024711-76.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9293,7 +8785,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
@@ -9308,17 +8800,17 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0013636-82.2021.8.17.2480</t>
+          <t>0126110-70.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9343,17 +8835,17 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0025225-84.2021.8.17.3090</t>
+          <t>0024858-97.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9378,17 +8870,17 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0012488-18.2021.8.17.2001</t>
+          <t>0157366-65.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9413,32 +8905,34 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>147</v>
-      </c>
-      <c r="C200" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="C200" t="n">
+        <v>20</v>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0000485-80.2018.8.17.2730</t>
+          <t>0004134-80.2025.8.17.2480</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>31/05/2025</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201">
@@ -9448,32 +8942,34 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>148</v>
-      </c>
-      <c r="C201" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C201" t="n">
+        <v>21</v>
+      </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0010172-55.2021.8.17.2640</t>
+          <t>0010739-65.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202">
@@ -9483,22 +8979,22 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0036173-20.2022.8.17.2001</t>
+          <t>0000141-46.2015.8.17.0001</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9508,7 +9004,7 @@
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203">
@@ -9518,22 +9014,22 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0049199-21.2012.8.17.0810</t>
+          <t>0013479-62.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -9543,7 +9039,7 @@
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204">
@@ -9553,32 +9049,34 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>151</v>
-      </c>
-      <c r="C204" t="inlineStr"/>
+        <v>152</v>
+      </c>
+      <c r="C204" t="n">
+        <v>22</v>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0024711-76.2016.8.17.2001</t>
+          <t>0013278-65.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205">
@@ -9588,32 +9086,34 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>152</v>
-      </c>
-      <c r="C205" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="C205" t="n">
+        <v>23</v>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0126110-70.2024.8.17.2001</t>
+          <t>0008630-73.2022.8.17.3090</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206">
@@ -9623,22 +9123,22 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0024858-97.2019.8.17.2001</t>
+          <t>0022647-49.2018.8.17.8201</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -9648,7 +9148,7 @@
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207">
@@ -9658,32 +9158,34 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>154</v>
-      </c>
-      <c r="C207" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="C207" t="n">
+        <v>18</v>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0157366-65.2023.8.17.2001</t>
+          <t>0002926-17.2020.8.17.2810</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208">
@@ -9693,34 +9195,32 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>155</v>
-      </c>
-      <c r="C208" t="n">
-        <v>20</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0004134-80.2025.8.17.2480</t>
+          <t>0009988-79.2018.8.17.2810</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209">
@@ -9730,19 +9230,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C209" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0010739-65.2019.8.17.3090</t>
+          <t>0088829-17.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9767,17 +9267,17 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0000141-46.2015.8.17.0001</t>
+          <t>0132006-47.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9802,12 +9302,12 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>0013479-62.2019.8.17.2001</t>
+          <t>0015345-66.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -9837,19 +9337,17 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>159</v>
-      </c>
-      <c r="C212" t="n">
-        <v>22</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0013278-65.2022.8.17.2001</t>
+          <t>0015043-45.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9859,7 +9357,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -9874,19 +9372,17 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>160</v>
-      </c>
-      <c r="C213" t="n">
-        <v>23</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>0008630-73.2022.8.17.3090</t>
+          <t>0000003-14.2015.8.17.2480</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9896,7 +9392,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
@@ -9911,17 +9407,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>161</v>
-      </c>
-      <c r="C214" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="C214" t="n">
+        <v>19</v>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>0022647-49.2018.8.17.8201</t>
+          <t>0009976-05.2021.8.17.2990</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9931,7 +9429,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
@@ -9946,19 +9444,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C215" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>0002926-17.2020.8.17.2810</t>
+          <t>0014938-45.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9983,17 +9481,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>163</v>
-      </c>
-      <c r="C216" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="C216" t="n">
+        <v>25</v>
+      </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>0009988-79.2018.8.17.2810</t>
+          <t>0030662-12.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10003,7 +9503,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -10018,19 +9518,17 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>164</v>
-      </c>
-      <c r="C217" t="n">
-        <v>24</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>0088829-17.2023.8.17.2001</t>
+          <t>0003628-74.2009.8.17.0990</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10040,7 +9538,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -10055,17 +9553,17 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0132006-47.2018.8.17.2990</t>
+          <t>0001870-75.2022.8.17.2810</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -10090,17 +9588,17 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>0015345-66.2023.8.17.2001</t>
+          <t>0016321-52.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10121,26 +9619,26 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>0015043-45.2023.8.17.3130</t>
+          <t>0000300-80.2025.8.17.3220</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Centro Judiciário de Solução de Conflitos e Cidadania de Salgueiro</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -10150,292 +9648,6 @@
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>168</v>
-      </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>0000003-14.2015.8.17.2480</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>169</v>
-      </c>
-      <c r="C222" t="n">
-        <v>20</v>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>0009976-05.2021.8.17.2990</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Super prioridade</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>170</v>
-      </c>
-      <c r="C223" t="n">
-        <v>21</v>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>0014938-45.2015.8.17.0480</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Super prioridade</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>171</v>
-      </c>
-      <c r="C224" t="n">
-        <v>25</v>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>0030662-12.2020.8.17.2001</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Prioridade Legal</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>172</v>
-      </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>0003628-74.2009.8.17.0990</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>173</v>
-      </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>0001870-75.2022.8.17.2810</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>4ª CC</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>174</v>
-      </c>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>0016321-52.2021.8.17.3130</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>02/06/2025</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>7ª CC</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>57</v>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>0000300-80.2025.8.17.3220</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Centro Judiciário de Solução de Conflitos e Cidadania de Salgueiro</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>28/05/2025</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Sem prioridade</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="n">
         <v>20</v>
       </c>
     </row>

--- a/alerta_processos.xlsx
+++ b/alerta_processos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -621,12 +621,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0001616-69.2018.8.17.2640</t>
+          <t>0000788-10.2017.8.17.2640</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3ª Vara Cível da Comarca de Garanhuns</t>
+          <t>2ª Vara Cível da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -663,12 +663,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0000788-10.2017.8.17.2640</t>
+          <t>0001319-13.2025.8.17.2480</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Garanhuns</t>
+          <t>6ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -705,12 +705,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0001319-13.2025.8.17.2480</t>
+          <t>0008497-68.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6ª Vara Cível da Comarca de Caruaru</t>
+          <t>Seção A da 21ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -744,15 +744,17 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0008497-68.2020.8.17.2001</t>
+          <t>0012055-95.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seção A da 21ª Vara Cível da Capital</t>
+          <t>2ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -762,7 +764,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -771,10 +773,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -786,12 +788,10 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0012055-95.2022.8.17.2480</t>
+          <t>0002021-27.2023.8.17.2480</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -833,17 +833,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0002021-27.2023.8.17.2480</t>
+          <t>0060611-81.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2ª Vara Cível da Comarca de Caruaru</t>
+          <t>Seção B da 36ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -860,7 +860,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -872,39 +872,37 @@
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0025713-76.2019.8.17.2001</t>
+          <t>0013423-53.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seção A da 24ª Vara Cível da Capital</t>
+          <t>Seção A da 36ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jonas Ferreira Da Paixao</t>
+          <t>Núcleo Especial</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -916,37 +914,39 @@
       <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0060611-81.2020.8.17.2001</t>
+          <t>0011034-76.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seção B da 36ª Vara Cível da Capital</t>
+          <t>Seção A da 5ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Juliane De Oliveira Maciel</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -961,17 +961,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0013423-53.2024.8.17.2001</t>
+          <t>0006414-34.2019.8.17.2480</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seção A da 36ª Vara Cível da Capital</t>
+          <t>3ª Vara Cível da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -981,14 +981,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Núcleo Especial</t>
+          <t>Juliane De Oliveira Maciel</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -1000,27 +1000,25 @@
       <c r="B14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0029863-71.2017.8.17.2001</t>
+          <t>0033738-15.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seção A da 4ª Vara Cível da Capital</t>
+          <t>Seção A da 16ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1032,7 +1030,7 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1047,17 +1045,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0001926-63.2016.8.17.2990</t>
+          <t>0127663-65.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5ª Vara Cível da Comarca de Olinda</t>
+          <t>Seção B da 7ª Vara Cível da Capital</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1067,14 +1065,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nathalia Fontenele Lima</t>
+          <t>Juliane De Oliveira Maciel</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1089,17 +1087,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0148031-96.2009.8.17.0001</t>
+          <t>0057541-27.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1109,14 +1107,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nathalia Fontenele Lima</t>
+          <t>Juliane De Oliveira Maciel</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1155,10 +1153,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1199,35 +1197,35 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0001672-51.2011.8.17.0570</t>
+          <t>0002047-64.2023.8.17.3340</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1ª Vara da Comarca de Escada</t>
+          <t>1ª Vara da Comarca de São José do Egito</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>20/05/2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1237,14 +1235,56 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Gustavo Mendes Da Hora</t>
+          <t>Valnete Lima Do Espirito Santo</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6ª CCJ</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0002453-80.2023.8.17.2210</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2ª Vara Cível da Comarca de Araripina</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>20/05/2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jose Carlos Ferreira Da Silva Junior</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I250"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1315,7 +1355,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -1340,7 +1380,7 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1350,7 +1390,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -1375,7 +1415,7 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1385,7 +1425,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -1410,32 +1450,32 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0045746-59.2008.8.17.0001</t>
+          <t>0009736-05.2018.8.17.8201</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1445,67 +1485,69 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0003033-30.2025.8.17.2990</t>
+          <t>0011014-10.2021.8.17.2810</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0006057-61.2015.8.17.0001</t>
+          <t>0006428-48.2012.8.17.0480</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1515,32 +1557,32 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0025576-94.2019.8.17.2001</t>
+          <t>0017700-14.2015.8.17.0810</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1550,32 +1592,32 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0017917-39.2016.8.17.2001</t>
+          <t>0000849-23.2016.8.17.2730</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1585,32 +1627,32 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0012736-57.2016.8.17.2001</t>
+          <t>0025688-32.2017.8.17.2810</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1620,32 +1662,32 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0005937-23.2025.8.17.2990</t>
+          <t>0123559-25.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1655,32 +1697,32 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0007385-31.2025.8.17.2990</t>
+          <t>0000093-41.2017.8.17.3130</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1690,67 +1732,69 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0142012-74.2009.8.17.0001</t>
+          <t>0022227-83.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0022319-28.2024.8.17.2990</t>
+          <t>0004439-87.2022.8.17.3250</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1760,67 +1804,69 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0009389-41.2025.8.17.2990</t>
+          <t>0000184-90.2025.8.17.2180</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>Vara Única da Comarca de Altinho</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0004140-79.2019.8.17.2001</t>
+          <t>0002337-77.2022.8.17.5001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1830,32 +1876,32 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0055460-96.2015.8.17.0001</t>
+          <t>0001432-88.2010.8.17.1090</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>2ª Vara Criminal da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1865,69 +1911,67 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79</v>
-      </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0021599-21.2024.8.17.2001</t>
+          <t>0000908-17.2015.8.17.0670</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>Vara Criminal da Comarca de Gravatá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0078744-69.2023.8.17.2001</t>
+          <t>0005016-50.2022.8.17.5001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1937,69 +1981,67 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
-      </c>
-      <c r="C20" t="n">
-        <v>29</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0043357-25.2022.8.17.2810</t>
+          <t>0009002-45.2020.8.17.0001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2ª Vara de Família e Registro Civil da Comarca de Jaboatão dos Guararapes</t>
+          <t>13ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0057037-11.2024.8.17.2001</t>
+          <t>0002979-14.2023.8.17.5810</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2009,32 +2051,32 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0005715-95.2012.8.17.0990</t>
+          <t>0001410-65.2020.8.17.0480</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vara de Sucessões e Registros Públicos da Comarca de Olinda</t>
+          <t>2ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2044,32 +2086,32 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0076618-81.2013.8.17.0001</t>
+          <t>0011659-51.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2079,32 +2121,32 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0045038-33.2013.8.17.0001</t>
+          <t>0001332-37.2021.8.17.0480</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>3ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2114,32 +2156,32 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0025427-94.2013.8.17.0001</t>
+          <t>0001245-07.2024.8.17.4480</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3ª Vara de Sucessões e Registros Públicos da Capital</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2149,32 +2191,32 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0000622-31.2014.8.17.1460</t>
+          <t>0002243-43.2022.8.17.4480</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Taquaritinga do Norte</t>
+          <t>4ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2184,32 +2226,32 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0000490-27.2024.8.17.2590</t>
+          <t>0000680-13.2019.8.17.0990</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Feira Nova</t>
+          <t>3ª Vara Criminal da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2219,32 +2261,32 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0000017-12.2020.8.17.2160</t>
+          <t>0002342-42.2018.8.17.1250</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de Alagoinha</t>
+          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2254,27 +2296,27 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0000312-54.2020.8.17.3290</t>
+          <t>0009496-07.2020.8.17.0001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vara Única da Comarca de São Caetano</t>
+          <t>4ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2289,7 +2331,7 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -2299,22 +2341,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0001017-09.2021.8.17.0480</t>
+          <t>0015715-70.2019.8.17.0001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>17ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2334,22 +2376,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0001935-30.2021.8.17.5001</t>
+          <t>0000213-04.2020.8.17.0730</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>Vara Criminal da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2369,22 +2411,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0000758-24.2021.8.17.4001</t>
+          <t>0006395-48.2018.8.17.0480</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2404,22 +2446,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0008778-96.2018.8.17.0480</t>
+          <t>0004011-26.2020.8.17.0001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
+          <t>11ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2439,22 +2481,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0001201-96.2020.8.17.0480</t>
+          <t>0000155-91.2022.8.17.5980</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara Criminal da Comarca de Carpina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2474,22 +2516,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0001033-94.2020.8.17.0480</t>
+          <t>0018282-11.2018.8.17.0001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>3ª Vara do Tribunal do Júri Capital</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2509,22 +2551,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0004750-51.2019.8.17.0480</t>
+          <t>0000606-43.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2544,22 +2586,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0002707-54.2022.8.17.5810</t>
+          <t>0006349-93.2023.8.17.4001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
+          <t>9ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2579,12 +2621,12 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0000153-19.2023.8.17.2640</t>
+          <t>0001001-94.2020.8.17.0640</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2594,7 +2636,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2614,22 +2656,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0000094-82.2020.8.17.1590</t>
+          <t>0001170-48.2022.8.17.5640</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2649,22 +2691,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0000458-42.2021.8.17.1130</t>
+          <t>0043154-88.2018.8.17.0810</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca Petrolina</t>
+          <t>2ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2684,22 +2726,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0004665-30.2023.8.17.3130</t>
+          <t>0005117-55.2019.8.17.0810</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca Petrolina</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2719,22 +2761,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0023121-52.2022.8.17.2810</t>
+          <t>0007267-09.2019.8.17.0810</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2754,22 +2796,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0000601-30.2011.8.17.0500</t>
+          <t>0002102-12.2023.8.17.4990</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>1ª Vara Criminal da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2789,22 +2831,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0010269-79.2003.8.17.1090</t>
+          <t>0000272-34.2023.8.17.5920</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Paulista</t>
+          <t>Vara Criminal da Comarca de Surubim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2824,22 +2866,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0001454-89.2020.8.17.0640</t>
+          <t>0019739-18.2014.8.17.0810</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2859,22 +2901,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0002337-77.2022.8.17.5001</t>
+          <t>0024592-06.2022.8.17.2810</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2894,22 +2936,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0001432-88.2010.8.17.1090</t>
+          <t>0000204-39.2021.8.17.5990</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Paulista</t>
+          <t>1ª Vara Criminal da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2929,22 +2971,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0000908-17.2015.8.17.0670</t>
+          <t>0001844-29.2019.8.17.0920</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Gravatá</t>
+          <t>Vara Criminal da Comarca de Limoeiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2964,22 +3006,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0005016-50.2022.8.17.5001</t>
+          <t>0008281-79.2022.8.17.2990</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Olinda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2999,22 +3041,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0009002-45.2020.8.17.0001</t>
+          <t>0000325-19.2019.8.17.0920</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13ª Vara Criminal da Capital</t>
+          <t>Vara Criminal da Comarca de Surubim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3034,22 +3076,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0002979-14.2023.8.17.5810</t>
+          <t>0000105-49.2023.8.17.4810</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3069,22 +3111,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0001410-65.2020.8.17.0480</t>
+          <t>0002883-34.2021.8.17.0001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
+          <t>6ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3104,22 +3146,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0011659-51.2015.8.17.0480</t>
+          <t>0000706-81.2023.8.17.6030</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Caruaru</t>
+          <t>2ª Vara Criminal da Comarca de Palmares</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3139,22 +3181,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0001332-37.2021.8.17.0480</t>
+          <t>0002716-79.2023.8.17.5810</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Caruaru</t>
+          <t>3ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3174,22 +3216,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0001245-07.2024.8.17.4480</t>
+          <t>0004845-40.2018.8.17.0990</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>2ª Vara Criminal da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3199,7 +3241,7 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -3209,22 +3251,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0002243-43.2022.8.17.4480</t>
+          <t>0000781-58.2022.8.17.5480</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Comarca de Caruaru</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3234,7 +3276,7 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -3244,22 +3286,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0000680-13.2019.8.17.0990</t>
+          <t>0041309-21.2018.8.17.0810</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca de Olinda</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3269,7 +3311,7 @@
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -3279,22 +3321,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0002342-42.2018.8.17.1250</t>
+          <t>0022899-12.2018.8.17.0810</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Santa Cruz do Capibaribe</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3304,7 +3346,7 @@
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -3314,22 +3356,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0009496-07.2020.8.17.0001</t>
+          <t>0000366-82.2021.8.17.4810</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4ª Vara Criminal da Capital</t>
+          <t>3ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3349,22 +3391,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0015715-70.2019.8.17.0001</t>
+          <t>0004819-83.2019.8.17.0480</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>17ª Vara Criminal da Capital</t>
+          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3384,22 +3426,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0000213-04.2020.8.17.0730</t>
+          <t>0005925-80.2019.8.17.0480</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Ipojuca</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3419,22 +3461,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0006395-48.2018.8.17.0480</t>
+          <t>0000020-79.2016.8.17.0810</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Caruaru</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3454,22 +3496,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0004011-26.2020.8.17.0001</t>
+          <t>0024373-20.2018.8.17.0001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>11ª Vara Criminal da Capital</t>
+          <t>5ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3489,22 +3531,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0000155-91.2022.8.17.5980</t>
+          <t>0000322-69.2020.8.17.0810</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Carpina</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3524,22 +3566,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0018282-11.2018.8.17.0001</t>
+          <t>0001426-63.2022.8.17.5810</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3ª Vara do Tribunal do Júri Capital</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3559,22 +3601,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0000606-43.2022.8.17.2480</t>
+          <t>0020305-90.2019.8.17.0001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Caruaru</t>
+          <t>3ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3594,22 +3636,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0006349-93.2023.8.17.4001</t>
+          <t>0003457-26.2019.8.17.0810</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>9ª Vara Criminal da Capital</t>
+          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3629,22 +3671,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0001001-94.2020.8.17.0640</t>
+          <t>0005297-62.2023.8.17.4001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
+          <t>3ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3664,22 +3706,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0001170-48.2022.8.17.5640</t>
+          <t>0016635-04.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3699,22 +3741,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0043154-88.2018.8.17.0810</t>
+          <t>0007697-26.2020.8.17.0001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara Criminal da Capital</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3734,22 +3776,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0005117-55.2019.8.17.0810</t>
+          <t>0000272-91.2017.8.17.1410</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara Criminal da Comarca de Surubim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3769,22 +3811,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0007267-09.2019.8.17.0810</t>
+          <t>0001934-17.2023.8.17.5990</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara Criminal da Comarca de Abreu e Lima</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3804,22 +3846,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0002102-12.2023.8.17.4990</t>
+          <t>0001719-04.2016.8.17.0100</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Paulista</t>
+          <t>Vara Criminal da Comarca de Abreu e Lima</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3839,22 +3881,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0000272-34.2023.8.17.5920</t>
+          <t>0001051-36.2024.8.17.5990</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Surubim</t>
+          <t>Vara Criminal da Comarca de Abreu e Lima</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3874,22 +3916,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0019739-18.2014.8.17.0810</t>
+          <t>0002906-98.2022.8.17.3410</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara Criminal da Comarca de Surubim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3909,22 +3951,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0024592-06.2022.8.17.2810</t>
+          <t>0003338-65.2019.8.17.0810</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3944,22 +3986,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0000204-39.2021.8.17.5990</t>
+          <t>0004294-23.2015.8.17.0810</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1ª Vara Criminal da Comarca de Paulista</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3979,22 +4021,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0001844-29.2019.8.17.0920</t>
+          <t>0004416-60.2020.8.17.0810</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Limoeiro</t>
+          <t>1ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4014,22 +4056,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0008281-79.2022.8.17.2990</t>
+          <t>0000316-54.2022.8.17.5640</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vara de Violência Doméstica e Familiar Contra Mulher de Olinda</t>
+          <t>2ª Vara Criminal da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4049,22 +4091,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0000325-19.2019.8.17.0920</t>
+          <t>0001722-34.2018.8.17.0990</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vara Criminal da Comarca de Surubim</t>
+          <t>2ª Vara Criminal da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4084,22 +4126,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0000105-49.2023.8.17.4810</t>
+          <t>0000848-27.2018.8.17.0480</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara Criminal da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4115,26 +4157,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0002883-34.2021.8.17.0001</t>
+          <t>0020079-63.2020.8.17.2810</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6ª Vara Criminal da Capital</t>
+          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4144,32 +4186,32 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0000706-81.2023.8.17.6030</t>
+          <t>0023238-95.2003.8.17.0001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2ª Vara Criminal da Comarca de Palmares</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4179,32 +4221,32 @@
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0002716-79.2023.8.17.5810</t>
+          <t>0007041-04.2020.8.17.2480</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>3ª Vara Criminal da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4214,7 +4256,7 @@
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
@@ -4224,22 +4266,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0014331-85.2010.8.17.0810</t>
+          <t>0045830-60.2008.8.17.0001</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4249,7 +4291,7 @@
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
@@ -4259,34 +4301,32 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>12</v>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0020917-82.2019.8.17.2990</t>
+          <t>0006236-98.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
@@ -4296,22 +4336,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0042254-24.2018.8.17.2001</t>
+          <t>0101563-63.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4321,7 +4361,7 @@
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -4331,22 +4371,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0014773-52.2019.8.17.2001</t>
+          <t>0036036-54.2004.8.17.0001</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4356,7 +4396,7 @@
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -4366,22 +4406,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0000778-83.2016.8.17.0640</t>
+          <t>0063500-71.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4391,7 +4431,7 @@
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -4401,22 +4441,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0001024-13.2003.8.17.0001</t>
+          <t>0011919-81.2013.8.17.0001</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>4ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4426,7 +4466,7 @@
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
@@ -4436,22 +4476,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0016259-49.2005.8.17.0001</t>
+          <t>0071550-92.2022.8.17.2990</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4461,7 +4501,7 @@
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
@@ -4471,22 +4511,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0042363-32.2012.8.17.0810</t>
+          <t>0000939-18.2019.8.17.3250</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca de Santa Cruz do Capibaribe</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4496,7 +4536,7 @@
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -4506,22 +4546,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0030807-95.2022.8.17.2810</t>
+          <t>0001673-11.1998.8.17.0370</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4531,7 +4571,7 @@
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94">
@@ -4541,32 +4581,34 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>20</v>
-      </c>
-      <c r="C94" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0003058-60.2021.8.17.2480</t>
+          <t>0007935-60.2011.8.17.0001</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -4576,34 +4618,32 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>21</v>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0167080-83.2022.8.17.2001</t>
+          <t>0009536-96.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>23/05/2025</t>
+          <t>26/05/2025</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96">
@@ -4613,17 +4653,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>22</v>
-      </c>
-      <c r="C96" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0020079-63.2020.8.17.2810</t>
+          <t>0021227-49.2023.8.17.2990</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4633,12 +4675,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97">
@@ -4648,17 +4690,17 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0023238-95.2003.8.17.0001</t>
+          <t>0096778-29.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4673,7 +4715,7 @@
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98">
@@ -4683,17 +4725,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24</v>
-      </c>
-      <c r="C98" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0007041-04.2020.8.17.2480</t>
+          <t>0054788-92.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4703,12 +4747,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -4718,12 +4762,12 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0045830-60.2008.8.17.0001</t>
+          <t>0040404-96.2010.8.17.0001</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4743,7 +4787,7 @@
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100">
@@ -4753,17 +4797,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26</v>
-      </c>
-      <c r="C100" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0006236-98.2019.8.17.3090</t>
+          <t>0011449-86.2024.8.17.3130</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4773,12 +4819,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
@@ -4788,27 +4834,29 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>27</v>
-      </c>
-      <c r="C101" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0101563-63.2024.8.17.2001</t>
+          <t>0032180-34.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -4823,22 +4871,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0036036-54.2004.8.17.0001</t>
+          <t>0009823-18.2019.8.17.2480</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4858,27 +4906,29 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>29</v>
-      </c>
-      <c r="C103" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0063500-71.2021.8.17.2001</t>
+          <t>0133240-48.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4893,27 +4943,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>30</v>
-      </c>
-      <c r="C104" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0011919-81.2013.8.17.0001</t>
+          <t>0020055-68.2020.8.17.3090</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4928,22 +4980,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0071550-92.2022.8.17.2990</t>
+          <t>0043827-26.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4963,22 +5015,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0000939-18.2019.8.17.3250</t>
+          <t>0003306-41.2017.8.17.1130</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Santa Cruz do Capibaribe</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4998,22 +5050,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0001673-11.1998.8.17.0370</t>
+          <t>0010243-77.2011.8.17.1130</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5033,29 +5085,27 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>34</v>
-      </c>
-      <c r="C108" t="n">
-        <v>2</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0007935-60.2011.8.17.0001</t>
+          <t>0013275-55.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -5070,27 +5120,29 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>35</v>
-      </c>
-      <c r="C109" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0009536-96.2014.8.17.0001</t>
+          <t>0018948-58.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5105,29 +5157,27 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>36</v>
-      </c>
-      <c r="C110" t="n">
-        <v>2</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0021227-49.2023.8.17.2990</t>
+          <t>0022852-54.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5142,27 +5192,29 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>37</v>
-      </c>
-      <c r="C111" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0096778-29.2022.8.17.2001</t>
+          <t>0010765-59.2021.8.17.2810</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5177,29 +5229,29 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0054788-92.2021.8.17.2001</t>
+          <t>0114419-59.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5214,22 +5266,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0040404-96.2010.8.17.0001</t>
+          <t>0010702-70.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5249,29 +5301,27 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>40</v>
-      </c>
-      <c r="C114" t="n">
-        <v>4</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0011449-86.2024.8.17.3130</t>
+          <t>0004024-33.2018.8.17.2640</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>26/05/2025</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5286,19 +5336,17 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>41</v>
-      </c>
-      <c r="C115" t="n">
-        <v>5</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0032180-34.2021.8.17.3090</t>
+          <t>0030684-31.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5308,12 +5356,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116">
@@ -5323,17 +5371,17 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0009823-18.2019.8.17.2480</t>
+          <t>0004453-24.2023.8.17.2640</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5348,7 +5396,7 @@
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117">
@@ -5358,19 +5406,17 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>43</v>
-      </c>
-      <c r="C117" t="n">
-        <v>3</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0133240-48.2023.8.17.2001</t>
+          <t>0048248-68.2008.8.17.0001</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5380,12 +5426,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118">
@@ -5395,19 +5441,17 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>44</v>
-      </c>
-      <c r="C118" t="n">
-        <v>4</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0020055-68.2020.8.17.3090</t>
+          <t>0181715-07.2012.8.17.0001</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5417,12 +5461,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119">
@@ -5432,17 +5476,17 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0043827-26.2021.8.17.3090</t>
+          <t>0103809-43.2009.8.17.0001</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5457,7 +5501,7 @@
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120">
@@ -5467,17 +5511,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>46</v>
-      </c>
-      <c r="C120" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="C120" t="n">
+        <v>7</v>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0003306-41.2017.8.17.1130</t>
+          <t>0011234-12.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5487,12 +5533,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121">
@@ -5502,17 +5548,17 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0010243-77.2011.8.17.1130</t>
+          <t>0001493-27.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5527,7 +5573,7 @@
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122">
@@ -5537,17 +5583,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>48</v>
-      </c>
-      <c r="C122" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0013275-55.2021.8.17.3130</t>
+          <t>0125045-74.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5557,12 +5605,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123">
@@ -5572,19 +5620,17 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>49</v>
-      </c>
-      <c r="C123" t="n">
-        <v>5</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0018948-58.2023.8.17.3130</t>
+          <t>0002164-94.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5594,12 +5640,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
@@ -5609,17 +5655,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>50</v>
-      </c>
-      <c r="C124" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="C124" t="n">
+        <v>8</v>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0022852-54.2018.8.17.2001</t>
+          <t>0018968-75.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5629,12 +5677,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125">
@@ -5644,19 +5692,17 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>51</v>
-      </c>
-      <c r="C125" t="n">
-        <v>6</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0010765-59.2021.8.17.2810</t>
+          <t>0015291-78.2013.8.17.0990</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5666,12 +5712,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126">
@@ -5681,19 +5727,17 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52</v>
-      </c>
-      <c r="C126" t="n">
-        <v>7</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0114419-59.2024.8.17.2001</t>
+          <t>0004393-95.2017.8.17.2370</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5703,12 +5747,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127">
@@ -5718,17 +5762,17 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0010702-70.2020.8.17.2001</t>
+          <t>0004882-72.2015.8.17.0990</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1ª Vara de Acidentes de Trabalho da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5743,7 +5787,7 @@
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128">
@@ -5753,17 +5797,17 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0004024-33.2018.8.17.2640</t>
+          <t>0031751-64.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5778,7 +5822,7 @@
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129">
@@ -5788,17 +5832,17 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0030684-31.2024.8.17.2001</t>
+          <t>0012360-66.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5813,7 +5857,7 @@
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130">
@@ -5823,17 +5867,17 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0004453-24.2023.8.17.2640</t>
+          <t>0001470-28.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5848,7 +5892,7 @@
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131">
@@ -5858,12 +5902,12 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0048248-68.2008.8.17.0001</t>
+          <t>0019067-45.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5883,7 +5927,7 @@
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132">
@@ -5893,17 +5937,17 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0181715-07.2012.8.17.0001</t>
+          <t>0006929-57.2020.8.17.2990</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5918,7 +5962,7 @@
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133">
@@ -5928,22 +5972,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0103809-43.2009.8.17.0001</t>
+          <t>0162784-18.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5963,14 +6007,12 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>60</v>
-      </c>
-      <c r="C134" t="n">
-        <v>8</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0011234-12.2019.8.17.3090</t>
+          <t>0003563-70.2009.8.17.1090</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5980,12 +6022,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -6000,22 +6042,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0001493-27.2022.8.17.2480</t>
+          <t>0013399-19.2023.8.17.2370</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6035,29 +6077,27 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>62</v>
-      </c>
-      <c r="C136" t="n">
-        <v>6</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0125045-74.2023.8.17.2001</t>
+          <t>0144859-88.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6072,22 +6112,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0002164-94.2019.8.17.2370</t>
+          <t>0000474-60.2025.8.17.2001</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -6107,29 +6147,27 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>64</v>
-      </c>
-      <c r="C138" t="n">
-        <v>9</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0018968-75.2022.8.17.2001</t>
+          <t>0048893-58.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6144,22 +6182,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0015291-78.2013.8.17.0990</t>
+          <t>0021145-14.2020.8.17.3090</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6179,22 +6217,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0004393-95.2017.8.17.2370</t>
+          <t>0000049-02.2023.8.17.2810</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -6214,27 +6252,29 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>67</v>
-      </c>
-      <c r="C141" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="C141" t="n">
+        <v>9</v>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0004882-72.2015.8.17.0990</t>
+          <t>0030671-06.2019.8.17.2810</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6249,27 +6289,29 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>68</v>
-      </c>
-      <c r="C142" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="C142" t="n">
+        <v>10</v>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0031751-64.2019.8.17.2370</t>
+          <t>0043033-42.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -6284,22 +6326,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0012360-66.2019.8.17.2001</t>
+          <t>0004615-15.2008.8.17.1130</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6319,22 +6361,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0001470-28.2019.8.17.2370</t>
+          <t>0043131-25.2019.8.17.2810</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6354,27 +6396,29 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>71</v>
-      </c>
-      <c r="C145" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="C145" t="n">
+        <v>6</v>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0019067-45.2022.8.17.2001</t>
+          <t>0011001-50.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -6389,22 +6433,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0006929-57.2020.8.17.2990</t>
+          <t>0000979-38.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>27/05/2025</t>
+          <t>28/05/2025</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6424,17 +6468,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>73</v>
-      </c>
-      <c r="C147" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="C147" t="n">
+        <v>7</v>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0162784-18.2022.8.17.2001</t>
+          <t>0100659-14.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6444,12 +6490,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="148">
@@ -6459,17 +6505,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>74</v>
-      </c>
-      <c r="C148" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8</v>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0003563-70.2009.8.17.1090</t>
+          <t>0137949-29.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6479,12 +6527,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149">
@@ -6494,17 +6542,17 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0013399-19.2023.8.17.2370</t>
+          <t>0000542-67.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6519,7 +6567,7 @@
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150">
@@ -6529,17 +6577,17 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0144859-88.2018.8.17.2990</t>
+          <t>0044705-22.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6554,7 +6602,7 @@
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151">
@@ -6564,17 +6612,17 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0000474-60.2025.8.17.2001</t>
+          <t>0008273-86.2014.8.17.0370</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6589,7 +6637,7 @@
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
@@ -6599,17 +6647,17 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0048893-58.2018.8.17.2001</t>
+          <t>0002783-88.2011.8.17.0370</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6624,7 +6672,7 @@
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="153">
@@ -6634,17 +6682,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>79</v>
-      </c>
-      <c r="C153" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="C153" t="n">
+        <v>9</v>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0021145-14.2020.8.17.3090</t>
+          <t>0159662-60.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6654,12 +6704,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154">
@@ -6669,12 +6719,12 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0000049-02.2023.8.17.2810</t>
+          <t>0012715-75.2010.8.17.0810</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6684,7 +6734,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6704,29 +6754,27 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>81</v>
-      </c>
-      <c r="C155" t="n">
-        <v>10</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0030671-06.2019.8.17.2810</t>
+          <t>0157599-62.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -6741,29 +6789,27 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>82</v>
-      </c>
-      <c r="C156" t="n">
-        <v>11</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0043033-42.2019.8.17.2001</t>
+          <t>0025016-37.2002.8.17.0001</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -6778,27 +6824,29 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>83</v>
-      </c>
-      <c r="C157" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="C157" t="n">
+        <v>10</v>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0004615-15.2008.8.17.1130</t>
+          <t>0002608-75.2023.8.17.2730</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -6813,22 +6861,22 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0043131-25.2019.8.17.2810</t>
+          <t>0067928-62.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6848,29 +6896,27 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>85</v>
-      </c>
-      <c r="C159" t="n">
-        <v>7</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0011001-50.2023.8.17.3130</t>
+          <t>0002885-17.2012.8.17.0810</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -6885,27 +6931,29 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>86</v>
-      </c>
-      <c r="C160" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="C160" t="n">
+        <v>11</v>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0000979-38.2018.8.17.2990</t>
+          <t>0124150-16.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -6920,29 +6968,29 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0100659-14.2022.8.17.2001</t>
+          <t>0023241-29.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -6957,29 +7005,27 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>88</v>
-      </c>
-      <c r="C162" t="n">
-        <v>9</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0137949-29.2023.8.17.2001</t>
+          <t>0013450-94.2011.8.17.0480</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -6994,27 +7040,29 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>89</v>
-      </c>
-      <c r="C163" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="C163" t="n">
+        <v>12</v>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0000542-67.2021.8.17.2480</t>
+          <t>0076202-15.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -7029,22 +7077,22 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0044705-22.2018.8.17.2001</t>
+          <t>0055769-26.1992.8.17.0001</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara dos Executivos Fiscais Estaduais da Capital</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7064,27 +7112,29 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>91</v>
-      </c>
-      <c r="C165" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="C165" t="n">
+        <v>12</v>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0008273-86.2014.8.17.0370</t>
+          <t>0022778-58.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -7099,22 +7149,22 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0002783-88.2011.8.17.0370</t>
+          <t>0065967-53.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7134,29 +7184,27 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>93</v>
-      </c>
-      <c r="C167" t="n">
-        <v>10</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0159662-60.2023.8.17.2001</t>
+          <t>0006228-56.2007.8.17.0370</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -7171,17 +7219,17 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0012715-75.2010.8.17.0810</t>
+          <t>0044866-95.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7196,7 +7244,7 @@
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169">
@@ -7206,17 +7254,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>95</v>
-      </c>
-      <c r="C169" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="C169" t="n">
+        <v>13</v>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0157599-62.2023.8.17.2001</t>
+          <t>0018284-50.2023.8.17.3090</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7226,12 +7276,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170">
@@ -7241,17 +7291,17 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0025016-37.2002.8.17.0001</t>
+          <t>0028674-55.2018.8.17.3090</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7266,7 +7316,7 @@
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171">
@@ -7276,19 +7326,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C171" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0002608-75.2023.8.17.2730</t>
+          <t>0060648-06.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7303,7 +7353,7 @@
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172">
@@ -7313,17 +7363,17 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0067928-62.2022.8.17.2001</t>
+          <t>0039607-27.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7338,7 +7388,7 @@
       </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="173">
@@ -7348,17 +7398,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>99</v>
-      </c>
-      <c r="C173" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="C173" t="n">
+        <v>13</v>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0002885-17.2012.8.17.0810</t>
+          <t>0021501-36.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7368,12 +7420,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174">
@@ -7383,29 +7435,27 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>100</v>
-      </c>
-      <c r="C174" t="n">
-        <v>12</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0124150-16.2023.8.17.2001</t>
+          <t>0013621-60.2018.8.17.2370</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -7420,29 +7470,29 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C175" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0023241-29.2024.8.17.2001</t>
+          <t>0001813-07.2006.8.17.0001</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -7457,22 +7507,22 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0013450-94.2011.8.17.0480</t>
+          <t>0001455-02.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7492,29 +7542,27 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>103</v>
-      </c>
-      <c r="C177" t="n">
-        <v>13</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0076202-15.2022.8.17.2001</t>
+          <t>0005162-20.2024.8.17.2480</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -7529,22 +7577,22 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0055769-26.1992.8.17.0001</t>
+          <t>0005994-20.2010.8.17.1130</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1ª Vara dos Executivos Fiscais Estaduais da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7564,24 +7612,24 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C179" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0022778-58.2022.8.17.2001</t>
+          <t>0090486-57.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7601,22 +7649,22 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0065967-53.2014.8.17.0001</t>
+          <t>0013636-82.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7636,22 +7684,22 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0006228-56.2007.8.17.0370</t>
+          <t>0025225-84.2021.8.17.3090</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7671,22 +7719,22 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0044866-95.2019.8.17.2001</t>
+          <t>0012488-18.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7706,29 +7754,27 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>109</v>
-      </c>
-      <c r="C183" t="n">
-        <v>14</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0018284-50.2023.8.17.3090</t>
+          <t>0000485-80.2018.8.17.2730</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -7743,22 +7789,22 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0028674-55.2018.8.17.3090</t>
+          <t>0010172-55.2021.8.17.2640</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7778,14 +7824,12 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>111</v>
-      </c>
-      <c r="C185" t="n">
-        <v>15</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0060648-06.2023.8.17.2001</t>
+          <t>0036173-20.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7795,12 +7839,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -7815,22 +7859,22 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0039607-27.2016.8.17.2001</t>
+          <t>0049199-21.2012.8.17.0810</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7850,29 +7894,27 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>113</v>
-      </c>
-      <c r="C187" t="n">
-        <v>14</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0021501-36.2024.8.17.2001</t>
+          <t>0024711-76.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>30/05/2025</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -7887,17 +7929,17 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0013621-60.2018.8.17.2370</t>
+          <t>0126110-70.2024.8.17.2001</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7912,7 +7954,7 @@
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189">
@@ -7922,19 +7964,17 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>115</v>
-      </c>
-      <c r="C189" t="n">
-        <v>16</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0001813-07.2006.8.17.0001</t>
+          <t>0024858-97.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7944,12 +7984,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190">
@@ -7959,17 +7999,17 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0001455-02.2019.8.17.2001</t>
+          <t>0157366-65.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>5ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7984,7 +8024,7 @@
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191">
@@ -7994,12 +8034,14 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>117</v>
-      </c>
-      <c r="C191" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="C191" t="n">
+        <v>15</v>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0005162-20.2024.8.17.2480</t>
+          <t>0004134-80.2025.8.17.2480</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -8009,12 +8051,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>31/05/2025</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -8029,32 +8071,34 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>118</v>
-      </c>
-      <c r="C192" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="C192" t="n">
+        <v>16</v>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0005994-20.2010.8.17.1130</t>
+          <t>0010739-65.2019.8.17.3090</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193">
@@ -8064,34 +8108,32 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>119</v>
-      </c>
-      <c r="C193" t="n">
-        <v>15</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0090486-57.2024.8.17.2001</t>
+          <t>0000141-46.2015.8.17.0001</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194">
@@ -8101,22 +8143,22 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0013636-82.2021.8.17.2480</t>
+          <t>0013479-62.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -8126,7 +8168,7 @@
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195">
@@ -8136,32 +8178,34 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>121</v>
-      </c>
-      <c r="C195" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="C195" t="n">
+        <v>17</v>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0025225-84.2021.8.17.3090</t>
+          <t>0013278-65.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196">
@@ -8171,32 +8215,34 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>122</v>
-      </c>
-      <c r="C196" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="C196" t="n">
+        <v>18</v>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0012488-18.2021.8.17.2001</t>
+          <t>0008630-73.2022.8.17.3090</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197">
@@ -8206,22 +8252,22 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0000485-80.2018.8.17.2730</t>
+          <t>0022647-49.2018.8.17.8201</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8231,7 +8277,7 @@
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="198">
@@ -8241,32 +8287,34 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>124</v>
-      </c>
-      <c r="C198" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="C198" t="n">
+        <v>16</v>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0010172-55.2021.8.17.2640</t>
+          <t>0002926-17.2020.8.17.2810</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Garanhuns</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199">
@@ -8276,22 +8324,22 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0036173-20.2022.8.17.2001</t>
+          <t>0009988-79.2018.8.17.2810</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8301,7 +8349,7 @@
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200">
@@ -8311,32 +8359,34 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>126</v>
-      </c>
-      <c r="C200" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="C200" t="n">
+        <v>19</v>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0049199-21.2012.8.17.0810</t>
+          <t>0088829-17.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>8ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201">
@@ -8346,22 +8396,22 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0024711-76.2016.8.17.2001</t>
+          <t>0132006-47.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Ipojuca</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8371,7 +8421,7 @@
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202">
@@ -8381,22 +8431,22 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0126110-70.2024.8.17.2001</t>
+          <t>0015345-66.2023.8.17.2001</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8406,7 +8456,7 @@
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="203">
@@ -8416,22 +8466,22 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0024858-97.2019.8.17.2001</t>
+          <t>0015043-45.2023.8.17.3130</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8441,7 +8491,7 @@
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204">
@@ -8451,22 +8501,22 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0157366-65.2023.8.17.2001</t>
+          <t>0000003-14.2015.8.17.2480</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>5ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>30/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8476,7 +8526,7 @@
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="205">
@@ -8486,34 +8536,34 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C205" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0004134-80.2025.8.17.2480</t>
+          <t>0009976-05.2021.8.17.2990</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="206">
@@ -8523,19 +8573,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C206" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>0010739-65.2019.8.17.3090</t>
+          <t>0014938-45.2015.8.17.0480</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8545,12 +8595,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207">
@@ -8560,17 +8610,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>133</v>
-      </c>
-      <c r="C207" t="inlineStr"/>
+        <v>126</v>
+      </c>
+      <c r="C207" t="n">
+        <v>20</v>
+      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>0000141-46.2015.8.17.0001</t>
+          <t>0030662-12.2020.8.17.2001</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8580,12 +8632,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208">
@@ -8595,17 +8647,17 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>0013479-62.2019.8.17.2001</t>
+          <t>0003628-74.2009.8.17.0990</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8620,7 +8672,7 @@
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209">
@@ -8630,19 +8682,17 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>135</v>
-      </c>
-      <c r="C209" t="n">
-        <v>18</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0013278-65.2022.8.17.2001</t>
+          <t>0001870-75.2022.8.17.2810</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8652,12 +8702,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210">
@@ -8667,19 +8717,17 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>136</v>
-      </c>
-      <c r="C210" t="n">
-        <v>19</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>0008630-73.2022.8.17.3090</t>
+          <t>0016321-52.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8689,12 +8737,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="211">
@@ -8704,22 +8752,22 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>0022647-49.2018.8.17.8201</t>
+          <t>0003847-76.2011.8.17.0001</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -8739,29 +8787,27 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>138</v>
-      </c>
-      <c r="C212" t="n">
-        <v>17</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>0002926-17.2020.8.17.2810</t>
+          <t>0011859-62.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
@@ -8776,22 +8822,22 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>0009988-79.2018.8.17.2810</t>
+          <t>0014107-88.2021.8.17.3130</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8811,24 +8857,24 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C214" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>0088829-17.2023.8.17.2001</t>
+          <t>0019719-68.2023.8.17.2990</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>8ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8848,22 +8894,22 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>0132006-47.2018.8.17.2990</t>
+          <t>0030945-20.2024.8.17.8201</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -8883,27 +8929,29 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>142</v>
-      </c>
-      <c r="C216" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="C216" t="n">
+        <v>22</v>
+      </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>0015345-66.2023.8.17.2001</t>
+          <t>0025893-29.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Capital</t>
+          <t>4ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
@@ -8918,12 +8966,12 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>0015043-45.2023.8.17.3130</t>
+          <t>0008054-57.2022.8.17.3130</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8933,7 +8981,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8953,12 +9001,12 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>0000003-14.2015.8.17.2480</t>
+          <t>0003270-81.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8968,7 +9016,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -8988,29 +9036,29 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C219" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>0009976-05.2021.8.17.2990</t>
+          <t>0006798-11.2024.8.17.3130</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Prioridade Legal</t>
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
@@ -9025,29 +9073,27 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>146</v>
-      </c>
-      <c r="C220" t="n">
-        <v>19</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>0014938-45.2015.8.17.0480</t>
+          <t>0000297-11.2017.8.17.3090</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -9062,24 +9108,24 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C221" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>0030662-12.2020.8.17.2001</t>
+          <t>0005253-86.2019.8.17.2480</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -9099,22 +9145,22 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>0003628-74.2009.8.17.0990</t>
+          <t>0083714-83.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -9134,22 +9180,22 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>0001870-75.2022.8.17.2810</t>
+          <t>0002990-32.2009.8.17.1090</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Vara dos Executivos Fiscais da Comarca de Jaboatão dos Guararapes</t>
+          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -9169,12 +9215,12 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>0016321-52.2021.8.17.3130</t>
+          <t>0002086-81.2012.8.17.1130</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -9184,7 +9230,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>03/06/2025</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -9204,12 +9250,12 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>0003847-76.2011.8.17.0001</t>
+          <t>0043198-89.2019.8.17.2001</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -9229,7 +9275,7 @@
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="226">
@@ -9239,17 +9285,17 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>0011859-62.2021.8.17.2480</t>
+          <t>0007512-43.2011.8.17.0990</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -9264,7 +9310,7 @@
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="227">
@@ -9274,17 +9320,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>153</v>
-      </c>
-      <c r="C227" t="inlineStr"/>
+        <v>146</v>
+      </c>
+      <c r="C227" t="n">
+        <v>19</v>
+      </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>0014107-88.2021.8.17.3130</t>
+          <t>0021988-21.2015.8.17.2001</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9294,12 +9342,12 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228">
@@ -9309,19 +9357,17 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>154</v>
-      </c>
-      <c r="C228" t="n">
-        <v>22</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>0019719-68.2023.8.17.2990</t>
+          <t>0049368-48.2017.8.17.2001</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9331,12 +9377,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="229">
@@ -9346,12 +9392,12 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>0030945-20.2024.8.17.8201</t>
+          <t>0000060-04.2021.8.17.2001</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -9371,7 +9417,7 @@
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230">
@@ -9381,19 +9427,17 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>156</v>
-      </c>
-      <c r="C230" t="n">
-        <v>23</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>0025893-29.2018.8.17.2001</t>
+          <t>0013370-43.2022.8.17.2001</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>4ª Vara da Fazenda Pública da Capital</t>
+          <t>6ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9403,12 +9447,12 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231">
@@ -9418,17 +9462,17 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>0008054-57.2022.8.17.3130</t>
+          <t>0088266-24.2014.8.17.0001</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>7ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9443,7 +9487,7 @@
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="232">
@@ -9453,17 +9497,17 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>0003270-81.2021.8.17.2480</t>
+          <t>0008889-70.2017.8.17.2370</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9478,7 +9522,7 @@
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="233">
@@ -9488,19 +9532,17 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>159</v>
-      </c>
-      <c r="C233" t="n">
-        <v>24</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>0006798-11.2024.8.17.3130</t>
+          <t>0005393-10.2016.8.17.2001</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9510,12 +9552,12 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234">
@@ -9525,17 +9567,17 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0000297-11.2017.8.17.3090</t>
+          <t>0018931-56.2022.8.17.3130</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9550,7 +9592,7 @@
       </c>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235">
@@ -9560,19 +9602,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C235" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0005253-86.2019.8.17.2480</t>
+          <t>0053419-74.2019.8.17.2990</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9582,12 +9624,12 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Prioridade Legal</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236">
@@ -9597,22 +9639,22 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0083714-83.2021.8.17.2001</t>
+          <t>0019683-50.2015.8.17.0001</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9632,22 +9674,22 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0002990-32.2009.8.17.1090</t>
+          <t>0001494-87.2016.8.17.0001</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Paulista</t>
+          <t>1ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -9667,12 +9709,14 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>164</v>
-      </c>
-      <c r="C238" t="inlineStr"/>
+        <v>157</v>
+      </c>
+      <c r="C238" t="n">
+        <v>21</v>
+      </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>0002086-81.2012.8.17.1130</t>
+          <t>0017102-69.2024.8.17.3130</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -9682,12 +9726,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -9702,12 +9746,12 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0043198-89.2019.8.17.2001</t>
+          <t>0021032-74.2004.8.17.0001</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -9717,7 +9761,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9737,27 +9781,29 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>166</v>
-      </c>
-      <c r="C240" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="C240" t="n">
+        <v>22</v>
+      </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0007512-43.2011.8.17.0990</t>
+          <t>0071085-19.2017.8.17.2001</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>3ª Vara da Fazenda Pública da Capital</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -9772,24 +9818,24 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C241" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0021988-21.2015.8.17.2001</t>
+          <t>0146277-61.2018.8.17.2990</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>3ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Olinda</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9809,12 +9855,14 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>168</v>
-      </c>
-      <c r="C242" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="C242" t="n">
+        <v>24</v>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0049368-48.2017.8.17.2001</t>
+          <t>0060492-91.2018.8.17.2001</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -9824,12 +9872,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sem prioridade</t>
+          <t>Super prioridade</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -9844,22 +9892,22 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0000060-04.2021.8.17.2001</t>
+          <t>0013801-32.2021.8.17.2480</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -9879,22 +9927,22 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0013370-43.2022.8.17.2001</t>
+          <t>0009888-18.2016.8.17.2480</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>6ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -9914,22 +9962,22 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>0088266-24.2014.8.17.0001</t>
+          <t>0001437-91.2022.8.17.2480</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>7ª Vara da Fazenda Pública da Capital</t>
+          <t>1ª Vara da Fazenda Pública da Comarca de Caruaru</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -9949,12 +9997,12 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>0008889-70.2017.8.17.2370</t>
+          <t>0028171-26.2019.8.17.2370</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -9964,7 +10012,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -9984,22 +10032,22 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>0005393-10.2016.8.17.2001</t>
+          <t>0013509-91.2018.8.17.2370</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2ª Vara da Fazenda Pública da Capital</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -10019,22 +10067,22 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>0018931-56.2022.8.17.3130</t>
+          <t>0009850-06.2020.8.17.2370</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Vara da Fazenda Pública da Comarca de Petrolina</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -10054,29 +10102,27 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>175</v>
-      </c>
-      <c r="C249" t="n">
-        <v>21</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>0053419-74.2019.8.17.2990</t>
+          <t>0013926-19.2017.8.17.2810</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1ª Vara da Fazenda Pública da Comarca de Olinda</t>
+          <t>2ª Vara da Fazenda Pública da Comarca de Jaboatão dos Guararapes</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>03/06/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Super prioridade</t>
+          <t>Sem prioridade</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -10087,26 +10133,26 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>0000300-80.2025.8.17.3220</t>
+          <t>0000369-59.2007.8.17.0370</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Centro Judiciário de Solução de Conflitos e Cidadania de Salgueiro</t>
+          <t>Vara da Fazenda Pública da Comarca do Cabo de Santo Agostinho</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>28/05/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -10116,7 +10162,497 @@
       </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="n">
-        <v>21</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>73</v>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>0039747-74.2023.8.17.2370</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2ª Vara Cível da Comarca do Cabo de Santo Agostinho</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>74</v>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0000622-95.2021.8.17.3170</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Vara Única da Comarca de Quipapá</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>75</v>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0001181-90.2023.8.17.2100</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>1ª Vara Cível da Comarca de Abreu e Lima</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>76</v>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0001218-83.2024.8.17.2100</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>1ª Vara Cível da Comarca de Abreu e Lima</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>77</v>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0002879-68.2022.8.17.2100</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>1ª Vara Cível da Comarca de Abreu e Lima</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>78</v>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0000242-09.2020.8.17.3170</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Vara Única da Comarca de Quipapá</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>79</v>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0002086-53.2007.8.17.0420</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2ª Vara Cível da Comarca de Camaragibe</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>80</v>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0000471-38.2018.8.17.3590</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>3ª Vara Cível da Comarca Vitória Santo Antão</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>81</v>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0000220-18.2025.8.17.2218</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>1ª Vara Cível da Comarca de Goiana</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>82</v>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>0000297-87.2013.8.17.1170</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Vara Única da Comarca de Quipapá</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>83</v>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0000234-92.2024.8.17.4980</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2ª Vara da Comarca de Timbaúba</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>84</v>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0001345-72.2019.8.17.1590</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Vara Única da Comarca de Pombos</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>5ª CC</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>85</v>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0000022-38.2019.8.17.2170</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Vara Única da Comarca de Aliança</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>7ª CC</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>25</v>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0000300-80.2025.8.17.3220</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Centro Judiciário de Solução de Conflitos e Cidadania de Salgueiro</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>28/05/2025</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Sem prioridade</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
